--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125800427</v>
+        <v>125800395</v>
       </c>
       <c r="B2" t="n">
-        <v>58365</v>
+        <v>57301</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125800395</v>
+        <v>125800427</v>
       </c>
       <c r="B3" t="n">
-        <v>57301</v>
+        <v>58365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,35 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100063</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>125800427</v>
       </c>
       <c r="B3" t="n">
-        <v>58365</v>
+        <v>58366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>125800426</v>
       </c>
       <c r="B4" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>125800418</v>
       </c>
       <c r="B6" t="n">
-        <v>58083</v>
+        <v>58084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125800395</v>
+        <v>125800427</v>
       </c>
       <c r="B2" t="n">
-        <v>57301</v>
+        <v>58367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100063</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125800427</v>
+        <v>125800395</v>
       </c>
       <c r="B3" t="n">
-        <v>58366</v>
+        <v>57302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,31 +801,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
         <v>125800426</v>
       </c>
       <c r="B4" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>125800400</v>
       </c>
       <c r="B5" t="n">
-        <v>57597</v>
+        <v>57598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>125800418</v>
       </c>
       <c r="B6" t="n">
-        <v>58084</v>
+        <v>58085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>125800404</v>
       </c>
       <c r="B7" t="n">
-        <v>57645</v>
+        <v>57646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,6 +1363,130 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126229623</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57454</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nylund, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>445134</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6594891</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lungsund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En till två skärror spelade samtidigt med den amerikanska beckasinen.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Wallander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Wallander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125800427</v>
+        <v>125800395</v>
       </c>
       <c r="B2" t="n">
-        <v>58367</v>
+        <v>57302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125800395</v>
+        <v>125800427</v>
       </c>
       <c r="B3" t="n">
-        <v>57302</v>
+        <v>58367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,35 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100063</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125800395</v>
+        <v>125800427</v>
       </c>
       <c r="B2" t="n">
-        <v>57302</v>
+        <v>58367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100063</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125800427</v>
+        <v>125800395</v>
       </c>
       <c r="B3" t="n">
-        <v>58367</v>
+        <v>57302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,31 +801,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125800427</v>
+        <v>125800395</v>
       </c>
       <c r="B2" t="n">
-        <v>58367</v>
+        <v>57306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125800395</v>
+        <v>125800427</v>
       </c>
       <c r="B3" t="n">
-        <v>57302</v>
+        <v>58371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,35 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100063</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
         <v>125800426</v>
       </c>
       <c r="B4" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>125800400</v>
       </c>
       <c r="B5" t="n">
-        <v>57598</v>
+        <v>57602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>125800418</v>
       </c>
       <c r="B6" t="n">
-        <v>58085</v>
+        <v>58089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>125800404</v>
       </c>
       <c r="B7" t="n">
-        <v>57646</v>
+        <v>57650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>126229623</v>
       </c>
       <c r="B8" t="n">
-        <v>57454</v>
+        <v>57458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,6 +1487,125 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126362033</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57458</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tallbacken, Kungsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>445278</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6594743</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lungsund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Teet Sirotkin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Teet Sirotkin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125800395</v>
+        <v>125800427</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>58371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100063</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125800427</v>
+        <v>125800395</v>
       </c>
       <c r="B3" t="n">
-        <v>58371</v>
+        <v>57306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,31 +801,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125800427</v>
+        <v>125800395</v>
       </c>
       <c r="B2" t="n">
-        <v>58371</v>
+        <v>57306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125800395</v>
+        <v>125800427</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>58371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,35 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100063</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125800395</v>
+        <v>125800427</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>58374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100063</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125800427</v>
+        <v>125800395</v>
       </c>
       <c r="B3" t="n">
-        <v>58371</v>
+        <v>57307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,31 +801,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
         <v>125800426</v>
       </c>
       <c r="B4" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>125800400</v>
       </c>
       <c r="B5" t="n">
-        <v>57602</v>
+        <v>57603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>125800418</v>
       </c>
       <c r="B6" t="n">
-        <v>58089</v>
+        <v>58092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>125800404</v>
       </c>
       <c r="B7" t="n">
-        <v>57650</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>126229623</v>
       </c>
       <c r="B8" t="n">
-        <v>57458</v>
+        <v>57459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>126362033</v>
       </c>
       <c r="B9" t="n">
-        <v>57458</v>
+        <v>57459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,6 +1606,351 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126572427</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57069</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nylund, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>445203</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6594880</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lungsund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joakim Setterlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Setterlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126572425</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56964</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nylund, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>445203</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6594880</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lungsund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Setterlund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Setterlund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126572429</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57459</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nylund, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>445203</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6594880</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lungsund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Setterlund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Setterlund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24631-2024 artfynd.xlsx
+++ b/artfynd/A 24631-2024 artfynd.xlsx
@@ -1647,7 +1647,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nylund, Vrm</t>
+          <t>Kungsskogshyttan, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1762,7 +1762,7 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nylund, Vrm</t>
+          <t>Kungsskogshyttan, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1877,7 +1877,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nylund, Vrm</t>
+          <t>Kungsskogshyttan, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
